--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136340740</v>
       </c>
       <c r="B6" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136341595</v>
       </c>
       <c r="B7" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136340197</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
